--- a/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana</t>
+          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,11; 39,82</t>
+          <t>36,08; 40,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,93; 40,23</t>
+          <t>36,94; 40,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,09; 37,94</t>
+          <t>33,55; 37,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,22; 39,53</t>
+          <t>35,21; 39,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,27; 39,42</t>
+          <t>35,18; 39,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,98; 38,9</t>
+          <t>35,09; 38,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,98; 40,27</t>
+          <t>35,08; 40,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,86; 38,03</t>
+          <t>33,52; 38,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,39; 39,19</t>
+          <t>36,46; 39,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,39; 39,14</t>
+          <t>36,63; 39,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,95; 38,46</t>
+          <t>34,99; 38,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,41; 38,37</t>
+          <t>35,38; 38,34</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,58</t>
+          <t>38,24; 40,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,02; 38,19</t>
+          <t>34,83; 38,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,69; 38,64</t>
+          <t>35,58; 38,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,15; 37,81</t>
+          <t>34,96; 37,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,64; 40,86</t>
+          <t>38,62; 40,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,44; 39,46</t>
+          <t>36,5; 39,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,49; 39,15</t>
+          <t>36,41; 39,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,22; 37,3</t>
+          <t>34,43; 37,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,84; 40,42</t>
+          <t>38,8; 40,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 38,55</t>
+          <t>36,3; 38,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,52; 38,6</t>
+          <t>36,6; 38,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 37,18</t>
+          <t>35,13; 37,36</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,17; 40,8</t>
+          <t>36,44; 40,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,1; 39,31</t>
+          <t>35,05; 39,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,11; 38,06</t>
+          <t>34,2; 37,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,03; 38,49</t>
+          <t>35,04; 38,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,59; 39,33</t>
+          <t>35,47; 39,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,85; 39,67</t>
+          <t>35,7; 39,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,94; 39,46</t>
+          <t>36,09; 39,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,24; 39,16</t>
+          <t>36,22; 39,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,26; 39,23</t>
+          <t>36,48; 39,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 39,01</t>
+          <t>36,09; 38,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,84; 38,37</t>
+          <t>35,64; 38,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,2; 38,37</t>
+          <t>36,29; 38,48</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,86; 42,16</t>
+          <t>38,92; 42,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,39; 39,94</t>
+          <t>36,5; 39,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,66; 41,09</t>
+          <t>36,61; 41,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,03; 39,57</t>
+          <t>37,12; 39,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,52; 41,24</t>
+          <t>38,47; 41,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,17; 40,81</t>
+          <t>36,18; 40,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,79; 39,1</t>
+          <t>34,86; 39,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,6; 40,58</t>
+          <t>37,49; 40,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,12; 41,35</t>
+          <t>39,21; 41,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,89; 39,97</t>
+          <t>36,77; 39,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,51; 39,51</t>
+          <t>36,41; 39,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,76; 39,77</t>
+          <t>37,72; 39,75</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,55; 40,25</t>
+          <t>38,57; 40,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,54; 38,37</t>
+          <t>36,62; 38,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,0; 37,93</t>
+          <t>36,14; 38,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,58; 38,16</t>
+          <t>36,55; 38,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,13; 39,72</t>
+          <t>38,24; 39,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,86; 38,83</t>
+          <t>36,9; 38,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,76; 38,72</t>
+          <t>36,64; 38,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,5</t>
+          <t>36,97; 38,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,76</t>
+          <t>38,62; 39,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,05; 38,35</t>
+          <t>37,02; 38,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,73; 38,01</t>
+          <t>36,69; 37,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,17</t>
+          <t>37,01; 38,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,08; 40,08</t>
+          <t>36,06; 40,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,94; 40,4</t>
+          <t>36,95; 40,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,55; 37,8</t>
+          <t>33,52; 37,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,21; 39,53</t>
+          <t>35,19; 39,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,18; 39,39</t>
+          <t>35,28; 39,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,09; 38,87</t>
+          <t>34,92; 38,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,08; 40,15</t>
+          <t>35,12; 40,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,52; 38,01</t>
+          <t>33,83; 38,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,46; 39,26</t>
+          <t>36,25; 39,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,63; 39,11</t>
+          <t>36,54; 39,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,99; 38,33</t>
+          <t>34,97; 38,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,38; 38,34</t>
+          <t>35,32; 38,27</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,66</t>
+          <t>38,17; 40,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,83; 38,12</t>
+          <t>34,93; 38,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,58; 38,68</t>
+          <t>35,55; 38,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,96; 37,71</t>
+          <t>35,09; 37,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,62; 40,78</t>
+          <t>38,65; 40,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,5; 39,7</t>
+          <t>36,38; 39,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,41; 39,27</t>
+          <t>36,4; 39,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,43; 37,31</t>
+          <t>34,25; 37,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,8; 40,45</t>
+          <t>38,83; 40,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,3; 38,39</t>
+          <t>36,35; 38,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 38,52</t>
+          <t>36,64; 38,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,13; 37,36</t>
+          <t>35,16; 37,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,44; 40,69</t>
+          <t>36,47; 40,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,05; 39,21</t>
+          <t>35,03; 39,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,2; 37,86</t>
+          <t>34,34; 38,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,04; 38,53</t>
+          <t>35,09; 38,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 39,18</t>
+          <t>35,56; 39,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,7; 39,8</t>
+          <t>35,87; 39,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,09; 39,3</t>
+          <t>35,96; 39,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,22; 39,23</t>
+          <t>36,22; 39,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,48; 39,24</t>
+          <t>36,32; 39,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,09; 38,99</t>
+          <t>35,96; 38,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,64; 38,26</t>
+          <t>35,66; 38,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,29; 38,48</t>
+          <t>36,28; 38,56</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,92; 42,27</t>
+          <t>38,83; 42,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,5; 39,92</t>
+          <t>36,36; 39,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,61; 41,34</t>
+          <t>36,74; 41,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,12; 39,62</t>
+          <t>37,13; 39,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,47; 41,23</t>
+          <t>38,33; 41,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,18; 40,82</t>
+          <t>36,04; 40,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,86; 39,13</t>
+          <t>35,01; 39,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,49; 40,46</t>
+          <t>37,7; 40,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,21; 41,29</t>
+          <t>39,18; 41,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,77; 39,75</t>
+          <t>36,77; 39,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,41; 39,52</t>
+          <t>36,47; 39,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,72; 39,75</t>
+          <t>37,75; 39,81</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,57; 40,24</t>
+          <t>38,67; 40,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,62; 38,38</t>
+          <t>36,64; 38,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,14; 38,08</t>
+          <t>35,99; 37,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,55; 38,17</t>
+          <t>36,59; 38,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,24; 39,72</t>
+          <t>38,17; 39,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,9; 38,84</t>
+          <t>36,94; 38,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,48</t>
+          <t>36,64; 38,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,97; 38,59</t>
+          <t>36,83; 38,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,62; 39,71</t>
+          <t>38,64; 39,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,02; 38,35</t>
+          <t>37,05; 38,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,69; 37,96</t>
+          <t>36,66; 37,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,08</t>
+          <t>37,0; 38,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37,43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36,89</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>38,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>38,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>35,68</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,48</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,46</t>
+          <t>37,42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,0</t>
+          <t>37,16</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,06; 40,07</t>
+          <t>35,27; 39,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,95; 40,37</t>
+          <t>34,98; 38,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,52; 37,98</t>
+          <t>34,98; 40,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,19; 39,45</t>
+          <t>35,09; 38,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,28; 39,41</t>
+          <t>36,11; 39,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,92; 38,71</t>
+          <t>36,93; 40,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,12; 40,28</t>
+          <t>33,09; 37,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,83; 38,03</t>
+          <t>34,5; 39,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,1</t>
+          <t>36,39; 39,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,54; 39,12</t>
+          <t>36,39; 39,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,97; 38,41</t>
+          <t>34,95; 38,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,27</t>
+          <t>35,58; 38,46</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39,77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38,06</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37,94</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35,86</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>39,51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,63</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>37,15</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,77</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>38,06</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,94</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,03</t>
+          <t>36,96</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,3</t>
+          <t>36,4</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,17; 40,64</t>
+          <t>38,64; 40,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,93; 38,12</t>
+          <t>36,44; 39,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,55; 38,65</t>
+          <t>36,49; 39,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,09; 37,74</t>
+          <t>33,97; 37,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,65; 40,74</t>
+          <t>38,24; 40,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,38; 39,68</t>
+          <t>35,02; 38,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,4; 39,25</t>
+          <t>35,69; 38,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,25; 37,26</t>
+          <t>35,74; 38,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,83; 40,37</t>
+          <t>38,84; 40,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,35; 38,56</t>
+          <t>36,27; 38,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,58</t>
+          <t>36,52; 38,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 37,24</t>
+          <t>35,27; 37,3</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37,73</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,76</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38,02</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>38,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>37,14</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>36,2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36,7</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,45</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,73</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,76</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,92</t>
+          <t>36,71</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,4</t>
+          <t>37,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,47; 40,9</t>
+          <t>35,59; 39,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,03; 39,34</t>
+          <t>35,85; 39,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,34; 38,05</t>
+          <t>35,94; 39,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,09; 38,58</t>
+          <t>36,31; 39,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,56; 39,16</t>
+          <t>36,17; 40,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,87; 39,8</t>
+          <t>35,1; 39,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,96; 39,47</t>
+          <t>34,11; 38,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,22; 39,25</t>
+          <t>35,06; 38,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,32; 39,34</t>
+          <t>36,26; 39,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,96; 38,84</t>
+          <t>36,07; 39,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,66; 38,22</t>
+          <t>35,84; 38,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,28; 38,56</t>
+          <t>36,26; 38,47</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39,97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,53</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38,75</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>40,53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38,15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>38,81</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,97</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,53</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,24</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,01</t>
+          <t>38,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,72</t>
+          <t>38,5</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,83; 42,13</t>
+          <t>38,52; 41,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 39,88</t>
+          <t>36,17; 40,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,74; 41,31</t>
+          <t>34,79; 39,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,13; 39,6</t>
+          <t>37,39; 40,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,33; 41,25</t>
+          <t>38,86; 42,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 40,79</t>
+          <t>36,39; 39,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,01; 39,4</t>
+          <t>36,66; 41,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 40,8</t>
+          <t>36,89; 39,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,18; 41,34</t>
+          <t>39,12; 41,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,77; 39,87</t>
+          <t>36,89; 39,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,47; 39,54</t>
+          <t>36,51; 39,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,75; 39,81</t>
+          <t>37,52; 39,45</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38,96</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37,72</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>39,46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>37,51</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>37,03</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37,38</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>37,42</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,57</t>
+          <t>37,58</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,67; 40,31</t>
+          <t>38,13; 39,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,43</t>
+          <t>36,86; 38,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 37,95</t>
+          <t>36,76; 38,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,59; 38,2</t>
+          <t>36,86; 38,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,17; 39,66</t>
+          <t>38,55; 40,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,92</t>
+          <t>36,54; 38,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,54</t>
+          <t>36,0; 37,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,83; 38,5</t>
+          <t>36,67; 38,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,64; 39,72</t>
+          <t>38,59; 39,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,66; 37,99</t>
+          <t>36,73; 38,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,0; 38,19</t>
+          <t>37,03; 38,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
+          <t>Número medio de horas a la semana que la persona entrevistada trabaja habitualmente (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37,1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,64</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,68</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37,42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>37,85</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37,86</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36,62</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,16</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>37.42574432153624</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>37.09651770305134</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>37.47865599943869</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>36.89482330703387</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>38.25857490360939</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>38.63721475343201</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>35.68320550073056</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>37.42208222734209</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>37.84596124407152</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>37.86144413852655</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>36.61845191697079</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>37.16079703615732</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>35,27; 39,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>34,98; 38,9</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>34,98; 40,27</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35,09; 38,3</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>36,11; 39,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,93; 40,23</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,09; 37,94</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34,5; 39,42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36,39; 39,19</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36,39; 39,14</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34,95; 38,46</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,58; 38,46</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>35.26902738183097</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>34.98394679294001</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>34.97659841523546</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>35.0919756273403</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>36.10783843368447</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>36.92515277919144</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>33.08721479388358</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>34.50129314226147</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>36.3929315839793</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>36.38573439042256</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>34.95299971939826</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>35.57538554920563</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>39.41821010487296</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>38.90058672790931</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>40.27414545638902</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>38.2983016825619</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>39.82429257171744</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>40.22916392268188</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>37.94023462938944</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>39.42373641166931</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>39.19460604939254</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>39.13988655828823</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>38.46285903449743</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>38.46448967964784</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>39,77</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>38,06</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>37,94</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,86</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,51</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,63</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,15</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36,96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39,64</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37,4</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>36,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>38,64; 40,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36,44; 39,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36,49; 39,15</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33,97; 37,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38,24; 40,58</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,02; 38,19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,69; 38,64</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35,74; 38,12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38,84; 40,42</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36,27; 38,55</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36,52; 38,6</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,27; 37,3</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>39.77326876975578</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>38.05895826830816</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>37.93589627914049</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>35.86446061009443</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>39.51380877078502</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>36.62660078140353</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>37.14541755626832</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>36.96191957534191</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>39.64155693157905</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>37.400058127664</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>37.57559883070289</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>36.40146715716153</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>37,45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>37,73</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37,76</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,61</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,14</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,2</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36,71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37,91</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>37,44</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36,98</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>37,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>38.63832889802704</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>36.43992652218041</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>36.49064059154648</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>33.96707359185345</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>38.24425307018788</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>35.02385033683022</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>35.6878444470843</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>35.73579861211832</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>38.83563007585498</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>36.26618629563153</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>36.51662717723989</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>35.27408104971616</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>35,59; 39,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>35,85; 39,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35,94; 39,46</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>36,31; 39,32</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>36,17; 40,8</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>35,1; 39,31</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>34,11; 38,06</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35,06; 38,65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36,26; 39,23</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36,07; 39,01</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35,84; 38,37</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>36,26; 38,47</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>40.86144685650015</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>39.46339986582328</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>39.15314689394609</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>37.15620842634852</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>40.57579236176288</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>38.18873331496292</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>38.63710627981464</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>38.12406523003481</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>40.41633136660513</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>38.54768004757974</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>38.60385795711795</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>37.30489865517982</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>39,97</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>38,53</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,53</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,81</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38,22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40,25</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>38,33</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38,0</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>38,5</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>37.45305617895145</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>37.72600160910491</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>37.76438392897104</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>38.02235363359225</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>38.61393696165874</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>37.13636989057952</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>36.19573706733524</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>36.70863256181266</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>37.91082721866399</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>37.43930055953633</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>36.98410590601279</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>37.43054149701218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>38,52; 41,24</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36,17; 40,81</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34,79; 39,1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37,39; 40,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,86; 42,16</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,39; 39,94</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36,66; 41,09</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36,89; 39,47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>39,12; 41,35</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36,89; 39,97</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36,51; 39,51</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,52; 39,45</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>35.58816350575275</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>35.84736680208867</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>35.93902847512828</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>36.30562923699166</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>36.17166625937998</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>35.09682122030286</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>34.11499219031401</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>35.05670559869077</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>36.26201697938316</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>36.07196555565434</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>35.83822865545316</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>36.26071112823631</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>39.33268828826477</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>39.67102940050147</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>39.46117697266018</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>39.32006303162758</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>40.80185334552465</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>39.31291251012676</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>38.06110956426106</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>38.65237296936203</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>39.2261183319528</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>39.00719672828065</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>38.36981482553436</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>38.46834094666491</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>39.96613152831058</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>38.52672197004063</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>37.2440748643808</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>38.74925317827343</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>40.5266461995129</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>38.14807093282358</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>38.81106380495087</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>38.21579432281634</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>40.2487905793525</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>38.32930719696819</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>37.99588287603614</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>38.4997133622114</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>38.5172545730342</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>36.16629342656167</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>34.79092572990293</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>37.38867166296856</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>38.85718272072306</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>36.3851910838554</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>36.66367026746558</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>36.88931094845707</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>39.11828080804649</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>36.89239029126962</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>36.50989054638104</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>37.52314071374031</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>41.23961549919117</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>40.81302089607681</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>39.10017059528228</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>40.19344447727291</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>42.16040237940567</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>39.93674419996614</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>41.08752271492976</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>39.47155308367324</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>41.3510951890676</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>39.97490670616037</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>39.50842158995209</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>39.45119406496241</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>39,46</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,51</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,03</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37,42</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39,2</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37,71</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37,36</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>38,13; 39,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 38,83</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36,76; 38,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 38,45</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38,55; 40,25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,54; 38,37</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,0; 37,93</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36,67; 38,22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38,59; 39,76</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37,05; 38,35</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>36,73; 38,01</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,03; 38,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>38.9617474409111</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>37.90219074550711</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>37.65356141937377</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>37.71831790625583</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>39.45980613506651</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>37.51110710414096</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>37.02884430379743</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>37.42407225162071</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>39.20382566576855</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>37.71164114895484</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>37.35608325700891</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>37.57967040272774</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>38.12523773764376</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>36.86293348712334</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>36.75545481731248</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>36.86144092227822</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>38.5533698392418</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>36.54003255877122</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>35.99740135009402</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>36.66954540489485</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>38.58758848846494</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>37.04987776274685</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>36.73002015215267</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>37.02791775350198</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>39.72393772825984</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>38.82678992143239</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>38.72199535822551</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>38.45406183983179</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>40.24687479746343</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>38.37038867402762</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>37.92503434363419</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>38.21766268070953</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>39.75863437497605</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>38.35263565720574</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>38.01489188576743</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>38.17214592169135</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
